--- a/artfynd/A 8097-2025 artfynd.xlsx
+++ b/artfynd/A 8097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74268192</v>
       </c>
       <c r="B2" t="n">
-        <v>99339</v>
+        <v>99344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253396</v>
       </c>
       <c r="B3" t="n">
-        <v>99263</v>
+        <v>99268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8097-2025 artfynd.xlsx
+++ b/artfynd/A 8097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74268192</v>
       </c>
       <c r="B2" t="n">
-        <v>99344</v>
+        <v>99345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253396</v>
       </c>
       <c r="B3" t="n">
-        <v>99268</v>
+        <v>99269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8097-2025 artfynd.xlsx
+++ b/artfynd/A 8097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74268192</v>
       </c>
       <c r="B2" t="n">
-        <v>99345</v>
+        <v>99372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253396</v>
       </c>
       <c r="B3" t="n">
-        <v>99269</v>
+        <v>99296</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8097-2025 artfynd.xlsx
+++ b/artfynd/A 8097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74268192</v>
       </c>
       <c r="B2" t="n">
-        <v>99372</v>
+        <v>99378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253396</v>
       </c>
       <c r="B3" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8097-2025 artfynd.xlsx
+++ b/artfynd/A 8097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74268192</v>
       </c>
       <c r="B2" t="n">
-        <v>99378</v>
+        <v>99385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253396</v>
       </c>
       <c r="B3" t="n">
-        <v>99302</v>
+        <v>99309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8097-2025 artfynd.xlsx
+++ b/artfynd/A 8097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74268192</v>
       </c>
       <c r="B2" t="n">
-        <v>99385</v>
+        <v>99389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253396</v>
       </c>
       <c r="B3" t="n">
-        <v>99309</v>
+        <v>99313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8097-2025 artfynd.xlsx
+++ b/artfynd/A 8097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74268192</v>
       </c>
       <c r="B2" t="n">
-        <v>99389</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253396</v>
       </c>
       <c r="B3" t="n">
-        <v>99313</v>
+        <v>99320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8097-2025 artfynd.xlsx
+++ b/artfynd/A 8097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74268192</v>
       </c>
       <c r="B2" t="n">
-        <v>99399</v>
+        <v>99404</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253396</v>
       </c>
       <c r="B3" t="n">
-        <v>99323</v>
+        <v>99328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8097-2025 artfynd.xlsx
+++ b/artfynd/A 8097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74268192</v>
       </c>
       <c r="B2" t="n">
-        <v>99404</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253396</v>
       </c>
       <c r="B3" t="n">
-        <v>99328</v>
+        <v>99336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8097-2025 artfynd.xlsx
+++ b/artfynd/A 8097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74268192</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74253396</v>
       </c>
       <c r="B3" t="n">
-        <v>99336</v>
+        <v>99346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 8097-2025 artfynd.xlsx
+++ b/artfynd/A 8097-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74268192</v>
+        <v>74253396</v>
       </c>
       <c r="B2" t="n">
-        <v>99422</v>
+        <v>99802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222361</v>
+        <v>222322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hallebo 800 m NNV, Sm</t>
+          <t>L31 Hallebo 800 m NNV, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -740,17 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1989-01-01</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-01-01</t>
+          <t>1991-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E1h 1903. SOM: Carex pulicaris. LEG: Inger Bergqvist, Torsten Karlsson</t>
+          <t>Smålands flora 2007: KOO: 7E1h 1903. SOM: Carex hostiana. LEG: Inger Bergqvist, Torsten Karlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Fuktig blandskog</t>
+          <t>Fukt. blandskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74253396</v>
+        <v>74268192</v>
       </c>
       <c r="B3" t="n">
-        <v>99346</v>
+        <v>99878</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,27 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222322</v>
+        <v>222361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>L31 Hallebo 800 m NNV, Sm</t>
+          <t>Hallebo 800 m NNV, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -851,17 +851,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1987-01-01</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1991-12-31</t>
+          <t>1989-01-01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E1h 1903. SOM: Carex hostiana. LEG: Inger Bergqvist, Torsten Karlsson</t>
+          <t>Smålands flora 2007: KOO: 7E1h 1903. SOM: Carex pulicaris. LEG: Inger Bergqvist, Torsten Karlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Fukt. blandskog</t>
+          <t>Fuktig blandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
